--- a/stories/arbres/TREE-SEC-012.xlsx
+++ b/stories/arbres/TREE-SEC-012.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Adam va à l'école avec Papa. Adam reste près de l'adulte. Sa main tient la main de Papa, ou le manteau de Papa. Ses pieds marchent à côté. Maman a mis le cartable.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam tient les cubes dans le sac. Il reste près de l'adulte. Main de Papa, ou manteau. Pieds à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2237,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2408,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi une pomme. Les chaussures font toc toc. Papa a mis une pomme dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2599,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2713,6 +2770,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chat. Le cartable tape doux. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2937,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3108,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chien. Le vent est doux. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3275,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3446,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit la poule. La cloche sonne loin. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3613,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3784,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi un yaourt. Un oiseau chante. Papa a mis un yaourt dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3883,6 +3975,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4049,6 +4146,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chat. Le vent est doux. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4211,6 +4313,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4377,6 +4484,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chien. La cloche sonne loin. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4539,6 +4651,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4705,6 +4822,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit la poule. Ça sent le pain. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4867,6 +4989,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5033,6 +5160,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi un morceau de pain. Le cartable tape doux. Papa a mis un morceau de pain. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5219,6 +5351,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5385,6 +5522,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chat. La cloche sonne loin. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5547,6 +5689,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5713,6 +5860,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chien. Ça sent le pain. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5875,6 +6027,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6041,6 +6198,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit la poule. Les chaussures font toc toc. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6203,6 +6365,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6369,6 +6536,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Adam tient le livre. Il reste près de l'adulte. Main de Papa, ou manteau. Pieds à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6553,6 +6725,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
     </row>
@@ -6725,6 +6902,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6911,6 +7093,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7077,6 +7264,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi une pomme. Le vent est doux. Papa a mis une pomme dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,6 +7455,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7429,6 +7626,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chat. Le vent est doux. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7591,6 +7793,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7757,6 +7964,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chien. La cloche sonne loin. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7919,6 +8131,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8085,6 +8302,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit la poule. Ça sent le pain. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8247,6 +8469,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8413,6 +8640,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi un yaourt. La cloche sonne loin. Papa a mis un yaourt dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8599,6 +8831,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8765,6 +9002,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chat. La cloche sonne loin. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8927,6 +9169,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9093,6 +9340,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chien. Ça sent le pain. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9255,6 +9507,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9421,6 +9678,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit la poule. Les chaussures font toc toc. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9583,6 +9845,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9749,6 +10016,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi un morceau de pain. Ça sent le pain. Papa a mis un morceau de pain. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9935,6 +10207,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10101,6 +10378,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chat. Ça sent le pain. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10263,6 +10545,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10429,6 +10716,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chien. Les chaussures font toc toc. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10591,6 +10883,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10757,6 +11054,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit la poule. Un oiseau chante. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10919,6 +11221,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11085,6 +11392,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pense à la dînette, à la maison. Il reste près de l'adulte. Main de Papa, ou manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11269,6 +11581,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
     </row>
@@ -11441,6 +11758,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11627,6 +11949,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11793,6 +12120,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi une pomme. Les chaussures font toc toc. Papa a mis une pomme dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11979,6 +12311,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12145,6 +12482,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chat. La cloche sonne loin. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12307,6 +12649,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12473,6 +12820,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chien. Ça sent le pain. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12635,6 +12987,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12801,6 +13158,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit la poule. Les chaussures font toc toc. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12963,6 +13325,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13129,6 +13496,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi un yaourt. Un oiseau chante. Papa a mis un yaourt dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13315,6 +13687,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13481,6 +13858,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chat. Ça sent le pain. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13643,6 +14025,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13809,6 +14196,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chien. Les chaussures font toc toc. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13971,6 +14363,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14137,6 +14534,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit la poule. Un oiseau chante. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14299,6 +14701,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14465,6 +14872,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi un morceau de pain. Le cartable tape doux. Papa a mis un morceau de pain. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14651,6 +15063,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14817,6 +15234,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chat. Les chaussures font toc toc. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14979,6 +15401,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15145,6 +15572,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit le chien. Un oiseau chante. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15307,6 +15739,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15473,6 +15910,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Adam voit la poule. Le cartable tape doux. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15635,6 +16077,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15653,7 +16100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15670,6 +16117,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-012.xlsx
+++ b/stories/arbres/TREE-SEC-012.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Adam va à l'école avec Papa. Adam reste près de l'adulte. Sa main tient la main de Papa, ou le manteau de Papa. Ses pieds marchent à côté. Maman a mis le cartable.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Adam tient les cubes dans le sac. Il reste près de l'adulte. Main de Papa, ou manteau. Pieds à côté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2060,7 @@
           <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2252,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2424,7 @@
           <t>narrateur|Adam a choisi une pomme. Les chaussures font toc toc. Papa a mis une pomme dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2602,6 +2614,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2775,6 +2792,7 @@
           <t>narrateur|Adam voit le chat. Le cartable tape doux. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2942,6 +2960,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3113,6 +3132,11 @@
           <t>narrateur|Adam voit le chien. Le vent est doux. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3280,6 +3304,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3451,6 +3476,7 @@
           <t>narrateur|Adam voit la poule. La cloche sonne loin. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3618,6 +3644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3789,6 +3816,7 @@
           <t>narrateur|Adam a choisi un yaourt. Un oiseau chante. Papa a mis un yaourt dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3978,6 +4006,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4151,6 +4184,7 @@
           <t>narrateur|Adam voit le chat. Le vent est doux. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4318,6 +4352,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4489,6 +4524,11 @@
           <t>narrateur|Adam voit le chien. La cloche sonne loin. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4656,6 +4696,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4827,6 +4868,7 @@
           <t>narrateur|Adam voit la poule. Ça sent le pain. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4994,6 +5036,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5165,6 +5208,7 @@
           <t>narrateur|Adam a choisi un morceau de pain. Le cartable tape doux. Papa a mis un morceau de pain. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5354,6 +5398,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5527,6 +5576,7 @@
           <t>narrateur|Adam voit le chat. La cloche sonne loin. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5694,6 +5744,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5865,6 +5916,11 @@
           <t>narrateur|Adam voit le chien. Ça sent le pain. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6032,6 +6088,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6203,6 +6260,7 @@
           <t>narrateur|Adam voit la poule. Les chaussures font toc toc. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6370,6 +6428,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6541,6 +6600,7 @@
           <t>narrateur|Adam tient le livre. Il reste près de l'adulte. Main de Papa, ou manteau. Pieds à côté.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6732,6 +6792,7 @@
           <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6907,6 +6968,7 @@
           <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7098,6 +7160,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7269,6 +7332,7 @@
           <t>narrateur|Adam a choisi une pomme. Le vent est doux. Papa a mis une pomme dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7458,6 +7522,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7631,6 +7700,7 @@
           <t>narrateur|Adam voit le chat. Le vent est doux. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7798,6 +7868,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7969,6 +8040,11 @@
           <t>narrateur|Adam voit le chien. La cloche sonne loin. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8136,6 +8212,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8307,6 +8384,7 @@
           <t>narrateur|Adam voit la poule. Ça sent le pain. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8474,6 +8552,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8645,6 +8724,7 @@
           <t>narrateur|Adam a choisi un yaourt. La cloche sonne loin. Papa a mis un yaourt dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8834,6 +8914,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -9007,6 +9092,7 @@
           <t>narrateur|Adam voit le chat. La cloche sonne loin. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9174,6 +9260,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9345,6 +9432,11 @@
           <t>narrateur|Adam voit le chien. Ça sent le pain. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9512,6 +9604,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9683,6 +9776,7 @@
           <t>narrateur|Adam voit la poule. Les chaussures font toc toc. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9850,6 +9944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10021,6 +10116,7 @@
           <t>narrateur|Adam a choisi un morceau de pain. Ça sent le pain. Papa a mis un morceau de pain. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10210,6 +10306,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10383,6 +10484,7 @@
           <t>narrateur|Adam voit le chat. Ça sent le pain. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10550,6 +10652,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10721,6 +10824,11 @@
           <t>narrateur|Adam voit le chien. Les chaussures font toc toc. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10888,6 +10996,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11059,6 +11168,7 @@
           <t>narrateur|Adam voit la poule. Un oiseau chante. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11226,6 +11336,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11397,6 +11508,7 @@
           <t>narrateur|Adam pense à la dînette, à la maison. Il reste près de l'adulte. Main de Papa, ou manteau.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11588,6 +11700,7 @@
           <t>narrateur|On reste où ? Près de l'adulte.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11763,6 +11876,7 @@
           <t>narrateur|Oui. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam retient : près de l'adulte, main ou manteau. La main tient la main de Papa, ou le manteau de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11954,6 +12068,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12125,6 +12240,7 @@
           <t>narrateur|Adam a choisi une pomme. Les chaussures font toc toc. Papa a mis une pomme dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12314,6 +12430,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12487,6 +12608,7 @@
           <t>narrateur|Adam voit le chat. La cloche sonne loin. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12654,6 +12776,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12825,6 +12948,11 @@
           <t>narrateur|Adam voit le chien. Ça sent le pain. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12992,6 +13120,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13163,6 +13292,7 @@
           <t>narrateur|Adam voit la poule. Les chaussures font toc toc. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13330,6 +13460,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13501,6 +13632,7 @@
           <t>narrateur|Adam a choisi un yaourt. Un oiseau chante. Papa a mis un yaourt dans le sac. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13690,6 +13822,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13863,6 +14000,7 @@
           <t>narrateur|Adam voit le chat. Ça sent le pain. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14030,6 +14168,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14201,6 +14340,11 @@
           <t>narrateur|Adam voit le chien. Les chaussures font toc toc. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14368,6 +14512,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14539,6 +14684,7 @@
           <t>narrateur|Adam voit la poule. Un oiseau chante. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14706,6 +14852,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14877,6 +15024,7 @@
           <t>narrateur|Adam a choisi un morceau de pain. Le cartable tape doux. Papa a mis un morceau de pain. Adam reste près de l'adulte. Main ou manteau. La main tient la main de Papa, ou le manteau de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15066,6 +15214,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15239,6 +15392,7 @@
           <t>narrateur|Adam voit le chat. Les chaussures font toc toc. Le chat de l'école est sur un muret. Adam reste près de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15406,6 +15560,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15577,6 +15732,11 @@
           <t>narrateur|Adam voit le chien. Un oiseau chante. Le chien du voisin reste sur le pas de porte. Adam reste près de l'adulte. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15744,6 +15904,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15915,6 +16076,7 @@
           <t>narrateur|Adam voit la poule. Le cartable tape doux. La poule d'un jardin picore. Adam tient le manteau de Papa. On reste près de l'adulte. La main tient la main, ou le manteau. Les pieds marchent à côté. Adam dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16082,6 +16244,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16100,7 +16263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16124,6 +16287,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16325,6 +16502,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
